--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_unityProjects\ComputerBasics_DaniTech_Work\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityBasic_6\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0045878D-1073-4E56-B4AB-E337975A9ADA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34625B44-12F2-426D-9ABF-A5210D25E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18330" yWindow="1455" windowWidth="16980" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -45,39 +45,67 @@
     <t>Description</t>
   </si>
   <si>
-    <t>skill_fireball_01</t>
+    <t>CostSP</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_normalSword_01</t>
+    <t>Type</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>파이어볼</t>
+    <t>CastRange</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>검기 날리기</t>
+    <t>EffectList</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>불로 된 구체를 만들어 날린다.</t>
+    <t>int</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>적을 벨 수 있는 검기를 날린다.</t>
+    <t>string</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>skill_rest_coffee_01</t>
+    <t>string[]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>커피 마시기</t>
+    <t>skill_smash</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>커피를 볶아 마신다. 모든 상태이상이 해제된다.</t>
+    <t>skill_flyingswallow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>강타</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>강하게 때린다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>참새날기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>참새처럼 날아서 때린다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Active</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DAMAGE:1,HEAL:3</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>KNOCKBACK:2,DAMAGE:2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -164,7 +192,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -187,11 +215,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -216,6 +264,19 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -460,6 +521,18 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -471,21 +544,41 @@
       <c r="C3" s="2" t="s">
         <v>5</v>
       </c>
+      <c r="D3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>20</v>
+      </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
@@ -497,18 +590,26 @@
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3">
+        <v>3</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>21</v>
+      </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
@@ -519,15 +620,9 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="A6" s="5"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityMiniProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34625B44-12F2-426D-9ABF-A5210D25E7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA9291-23C6-4375-9858-7E873A027954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36765" yWindow="1125" windowWidth="15450" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -101,11 +101,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>DAMAGE:1,HEAL:3</t>
+    <t>KNOCKBACK:2,DAMAGE:2</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>KNOCKBACK:2,DAMAGE:2</t>
+    <t>DAMAGE:1,SELFHEAL:3</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -267,16 +267,15 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -577,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -607,8 +606,8 @@
       <c r="F5" s="3">
         <v>3</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>21</v>
+      <c r="G5" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityMiniProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA9291-23C6-4375-9858-7E873A027954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF15DD06-CAE7-45DE-B8AE-1162637CDAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36765" yWindow="1125" windowWidth="15450" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36765" yWindow="1125" windowWidth="18570" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -101,11 +101,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>KNOCKBACK:2,DAMAGE:2</t>
+    <t>DAMAGE:1,SELFHEAL:3</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>DAMAGE:1,SELFHEAL:3</t>
+    <t>DASHSLASH:3:5</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -576,7 +576,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -607,7 +607,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityMiniProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF15DD06-CAE7-45DE-B8AE-1162637CDAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B61DCAC-E304-466F-B9B4-F71C2E47A3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36765" yWindow="1125" windowWidth="18570" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33315" yWindow="675" windowWidth="22035" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>캐릭터 고유 ID</t>
   </si>
@@ -106,6 +106,22 @@
   </si>
   <si>
     <t>DASHSLASH:3:5</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>skill_walljump</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽점프</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벽을 박차고 반대 방향으로 도약한다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WALLJUMP:1</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -239,7 +255,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -274,6 +290,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -619,13 +641,27 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>25</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>

--- a/JsonConverter/ExcelFiles/Skill.xlsx
+++ b/JsonConverter/ExcelFiles/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\오즈_과제\UnityMiniProject2D\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B61DCAC-E304-466F-B9B4-F71C2E47A3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48A30138-B778-4682-9CFB-7039083D1EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33315" yWindow="675" windowWidth="22035" windowHeight="14175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -295,7 +295,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -620,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>19</v>
@@ -651,7 +651,7 @@
         <v>24</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>19</v>
